--- a/apps/frontend/src/__tests__/fixtures/rosterFormats/committee-export-2026-04-16.excerpt.xlsx
+++ b/apps/frontend/src/__tests__/fixtures/rosterFormats/committee-export-2026-04-16.excerpt.xlsx
@@ -32,9 +32,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="dd-mmm-yy"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -488,10 +487,10 @@
         <v>006</v>
       </c>
       <c r="D2" t="str">
-        <v>EMILIANO BRINI</v>
+        <v>EMERSON T BRAITHWAITE</v>
       </c>
       <c r="E2" t="str">
-        <v>21 SUTER TER</v>
+        <v>21 SUTTON TER</v>
       </c>
       <c r="F2" t="str">
         <v>ROCHESTER</v>
@@ -503,7 +502,7 @@
         <v>14620</v>
       </c>
       <c r="I2" t="str">
-        <v>(631) 600-3364</v>
+        <v>(631) 555-0164</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -512,7 +511,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>EMILIANO.BRINI@GMAIL.COM</v>
+        <v>EBRAITHWAITE@EXAMPLE.COM</v>
       </c>
       <c r="M2" t="str">
         <v>Democratic</v>
@@ -524,7 +523,7 @@
         <v>30655</v>
       </c>
       <c r="P2" t="str">
-        <v>100387573</v>
+        <v>900110001</v>
       </c>
       <c r="Q2" t="str">
         <v>LD 023</v>
@@ -565,10 +564,10 @@
         <v>015</v>
       </c>
       <c r="D3" t="str">
-        <v>DANIEL F BRENNAN</v>
+        <v>DANIELA F BRENNIGAN</v>
       </c>
       <c r="E3" t="str">
-        <v>316 WESTMINSTER RD</v>
+        <v>316 WESTGROVE RD</v>
       </c>
       <c r="F3" t="str">
         <v>ROCHESTER</v>
@@ -580,7 +579,7 @@
         <v>14607</v>
       </c>
       <c r="I3" t="str">
-        <v>(585) 415-2221</v>
+        <v>(585) 555-0122</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -595,13 +594,13 @@
         <v>Democratic</v>
       </c>
       <c r="N3" t="str">
-        <v>M</v>
+        <v>F</v>
       </c>
       <c r="O3">
         <v>31959</v>
       </c>
       <c r="P3" t="str">
-        <v>000241802</v>
+        <v>000910002</v>
       </c>
       <c r="Q3" t="str">
         <v>LD 023</v>
@@ -642,7 +641,7 @@
         <v>012</v>
       </c>
       <c r="D4" t="str">
-        <v>DENISE B FORSTER</v>
+        <v>DELIA B FORSGREN</v>
       </c>
       <c r="E4" t="str">
         <v>42 CLARKES XING</v>
@@ -657,7 +656,7 @@
         <v>14450</v>
       </c>
       <c r="I4" t="str">
-        <v>(585) 355-0536</v>
+        <v>(585) 555-0136</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -678,7 +677,7 @@
         <v>20516</v>
       </c>
       <c r="P4" t="str">
-        <v>018153116</v>
+        <v>018910003</v>
       </c>
       <c r="Q4" t="str">
         <v>Perinton</v>
@@ -719,10 +718,10 @@
         <v>006</v>
       </c>
       <c r="D5" t="str">
-        <v>TERESE M ABRAMS</v>
+        <v>TERRANCE M ABERNATHY</v>
       </c>
       <c r="E5" t="str">
-        <v>889 HIDDEN VALLEY RD</v>
+        <v>889 HIDDEN MEADOW RD</v>
       </c>
       <c r="F5" t="str">
         <v>ROCHESTER</v>
@@ -734,7 +733,7 @@
         <v>14624</v>
       </c>
       <c r="I5" t="str">
-        <v>(585) 594-2531</v>
+        <v>(585) 555-0131</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -743,19 +742,19 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>TABRAMS@ROCHESTER.RR.COM</v>
+        <v>TABERNATHY@EXAMPLE.COM</v>
       </c>
       <c r="M5" t="str">
         <v>Democratic</v>
       </c>
       <c r="N5" t="str">
-        <v>F</v>
+        <v>M</v>
       </c>
       <c r="O5">
         <v>22246</v>
       </c>
       <c r="P5" t="str">
-        <v>020090848</v>
+        <v>020910004</v>
       </c>
       <c r="Q5" t="str">
         <v>Gates</v>
@@ -796,7 +795,7 @@
         <v>012</v>
       </c>
       <c r="D6" t="str">
-        <v>MAXIMILLIAN J GORDON</v>
+        <v>MAXIMILLIAN J GORLAND</v>
       </c>
       <c r="E6" t="str">
         <v>3 E JEFFERSON CIR</v>
@@ -811,7 +810,7 @@
         <v>14534</v>
       </c>
       <c r="I6" t="str">
-        <v>(585) 370-7900</v>
+        <v>(585) 555-0179</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -820,7 +819,7 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>MGORDON99@GMAIL.COM</v>
+        <v>MGORLAND@EXAMPLE.COM</v>
       </c>
       <c r="M6" t="str">
         <v>Democratic</v>
@@ -832,7 +831,7 @@
         <v>34122</v>
       </c>
       <c r="P6" t="str">
-        <v>100089814</v>
+        <v>900110005</v>
       </c>
       <c r="Q6" t="str">
         <v>Pittsford</v>
@@ -873,7 +872,7 @@
         <v>003</v>
       </c>
       <c r="D7" t="str">
-        <v>KILEY L BARZ</v>
+        <v>KIERA L BARLOWE</v>
       </c>
       <c r="E7" t="str">
         <v>156 HOOVER RD</v>
@@ -888,7 +887,7 @@
         <v>14617</v>
       </c>
       <c r="I7" t="str">
-        <v>(315) 521-4048</v>
+        <v>(315) 555-0148</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -897,7 +896,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>KILEYLYNN73@YAHOO.COM</v>
+        <v>KBARLOWE@EXAMPLE.COM</v>
       </c>
       <c r="M7" t="str">
         <v>Democratic</v>
@@ -909,7 +908,7 @@
         <v>30723</v>
       </c>
       <c r="P7" t="str">
-        <v>000248034</v>
+        <v>000910006</v>
       </c>
       <c r="Q7" t="str">
         <v>Irondequoit</v>
@@ -950,7 +949,7 @@
         <v>005</v>
       </c>
       <c r="D8" t="str">
-        <v>DAVID D CIESLINSKI</v>
+        <v>DAVID D CIESLAK</v>
       </c>
       <c r="E8" t="str">
         <v>229 W IVY ST</v>
@@ -986,7 +985,7 @@
         <v>27353</v>
       </c>
       <c r="P8" t="str">
-        <v>100044299</v>
+        <v>900110007</v>
       </c>
       <c r="Q8" t="str">
         <v>East Rochester</v>
@@ -1027,10 +1026,10 @@
         <v>002</v>
       </c>
       <c r="D9" t="str">
-        <v>KELLI JO EBERLE</v>
+        <v>KELSEY JO EBERHART</v>
       </c>
       <c r="E9" t="str">
-        <v>332 KEYES RD</v>
+        <v>332 KEYSTONE RD</v>
       </c>
       <c r="F9" t="str">
         <v>HONEOYE FALLS</v>
@@ -1042,7 +1041,7 @@
         <v>14472</v>
       </c>
       <c r="I9" t="str">
-        <v>(585) 533-9059</v>
+        <v>(585) 555-0159</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -1051,7 +1050,7 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>KJEBERLE@HOTMAIL.COM</v>
+        <v>KEBERHART@EXAMPLE.COM</v>
       </c>
       <c r="M9" t="str">
         <v>Democratic</v>
@@ -1063,7 +1062,7 @@
         <v>25737</v>
       </c>
       <c r="P9" t="str">
-        <v>002413455</v>
+        <v>002910008</v>
       </c>
       <c r="Q9" t="str">
         <v>Rush</v>
@@ -1104,7 +1103,7 @@
         <v>034</v>
       </c>
       <c r="D10" t="str">
-        <v>JONATHAN E KYLE</v>
+        <v>JONATHAN E KYLER</v>
       </c>
       <c r="E10" t="str">
         <v>63 KNOLLTOP DR</v>
@@ -1140,7 +1139,7 @@
         <v>29094</v>
       </c>
       <c r="P10" t="str">
-        <v>000255493</v>
+        <v>000910009</v>
       </c>
       <c r="Q10" t="str">
         <v>Brighton</v>
@@ -1181,7 +1180,7 @@
         <v>006</v>
       </c>
       <c r="D11" t="str">
-        <v>MARY C KIESSLING</v>
+        <v>MARIA C KESSLING</v>
       </c>
       <c r="E11" t="str">
         <v>7644 BUFFALO RD</v>
@@ -1196,7 +1195,7 @@
         <v>14416</v>
       </c>
       <c r="I11" t="str">
-        <v>(585) 474-3006</v>
+        <v>(585) 555-0106</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -1217,7 +1216,7 @@
         <v>21540</v>
       </c>
       <c r="P11" t="str">
-        <v>018158801</v>
+        <v>018910010</v>
       </c>
       <c r="Q11" t="str">
         <v>Riga</v>
@@ -1258,10 +1257,10 @@
         <v>003</v>
       </c>
       <c r="D12" t="str">
-        <v>DANIEL A FALTER</v>
+        <v>DANIEL A FALCONER</v>
       </c>
       <c r="E12" t="str">
-        <v>255 ROBERT QUIGLEY DR APT 1</v>
+        <v>255 ROBERT QUINN DR APT 1</v>
       </c>
       <c r="F12" t="str">
         <v>SCOTTSVILLE</v>
@@ -1273,7 +1272,7 @@
         <v>14546</v>
       </c>
       <c r="I12" t="str">
-        <v>(585) 967-6828</v>
+        <v>(585) 555-0128</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -1294,7 +1293,7 @@
         <v>36599</v>
       </c>
       <c r="P12" t="str">
-        <v>100309603</v>
+        <v>900110011</v>
       </c>
       <c r="Q12" t="str">
         <v>Wheatland</v>
@@ -1335,7 +1334,7 @@
         <v>002</v>
       </c>
       <c r="D13" t="str">
-        <v>SARAH E JOHNSTON</v>
+        <v>SARAH E JOHNSGARD</v>
       </c>
       <c r="E13" t="str">
         <v>4196 ROOSEVELT HWY</v>
@@ -1371,7 +1370,7 @@
         <v>26087</v>
       </c>
       <c r="P13" t="str">
-        <v>000168393</v>
+        <v>000910012</v>
       </c>
       <c r="Q13" t="str">
         <v>Hamlin</v>
@@ -1412,7 +1411,7 @@
         <v>010</v>
       </c>
       <c r="D14" t="str">
-        <v>JOANN B SHARP</v>
+        <v>JOANNA B SHARPE</v>
       </c>
       <c r="E14" t="str">
         <v>4987 LAKE RD</v>
@@ -1427,7 +1426,7 @@
         <v>14420</v>
       </c>
       <c r="I14" t="str">
-        <v>(678) 296-7798</v>
+        <v>(678) 555-0198</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -1436,7 +1435,7 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>JOANNBROWNSHARP@GMAIL.COM</v>
+        <v>JSHARPE@EXAMPLE.COM</v>
       </c>
       <c r="M14" t="str">
         <v>Democratic</v>
@@ -1448,7 +1447,7 @@
         <v>24499</v>
       </c>
       <c r="P14" t="str">
-        <v>100289721</v>
+        <v>900110013</v>
       </c>
       <c r="Q14" t="str">
         <v>Sweden</v>
@@ -1489,10 +1488,10 @@
         <v>005</v>
       </c>
       <c r="D15" t="str">
-        <v>FRANK FEMIA</v>
+        <v>FRANCO FEMBRIDGE</v>
       </c>
       <c r="E15" t="str">
-        <v>45 WAYNE DR</v>
+        <v>45 WAYLAND DR</v>
       </c>
       <c r="F15" t="str">
         <v>ROCHESTER</v>
@@ -1504,7 +1503,7 @@
         <v>14626</v>
       </c>
       <c r="I15" t="str">
-        <v>(585) 643-0475</v>
+        <v>(585) 555-0175</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -1525,7 +1524,7 @@
         <v>34739</v>
       </c>
       <c r="P15" t="str">
-        <v>100090879</v>
+        <v>900110014</v>
       </c>
       <c r="Q15" t="str">
         <v>Greece</v>
@@ -1566,7 +1565,7 @@
         <v>003</v>
       </c>
       <c r="D16" t="str">
-        <v>JON P GETZ</v>
+        <v>JONAH P GETTLER</v>
       </c>
       <c r="E16" t="str">
         <v>5 CENTER COURT LN</v>
@@ -1581,7 +1580,7 @@
         <v>14526</v>
       </c>
       <c r="I16" t="str">
-        <v>(585) 820-9291</v>
+        <v>(585) 555-0191</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1590,7 +1589,7 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>jongetz@jgetzlaw.com</v>
+        <v>jgettler@example.com</v>
       </c>
       <c r="M16" t="str">
         <v>Democratic</v>
@@ -1602,7 +1601,7 @@
         <v>24657</v>
       </c>
       <c r="P16" t="str">
-        <v>002645771</v>
+        <v>002910015</v>
       </c>
       <c r="Q16" t="str">
         <v>Penfield</v>
@@ -1643,7 +1642,7 @@
         <v>005</v>
       </c>
       <c r="D17" t="str">
-        <v>LINDA A BENOIT</v>
+        <v>LINNEA A BENNETTE</v>
       </c>
       <c r="E17" t="str">
         <v>2697 SWEDEN WALKER RD</v>
@@ -1658,7 +1657,7 @@
         <v>14420</v>
       </c>
       <c r="I17" t="str">
-        <v>(585) 637-3234</v>
+        <v>(585) 555-0134</v>
       </c>
       <c r="J17" t="str">
         <v/>
@@ -1667,7 +1666,7 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>MRSBUZ@ICLOUD.COM</v>
+        <v>LBENNETTE@EXAMPLE.COM</v>
       </c>
       <c r="M17" t="str">
         <v>Democratic</v>
@@ -1679,7 +1678,7 @@
         <v>22590</v>
       </c>
       <c r="P17" t="str">
-        <v>018683912</v>
+        <v>018910016</v>
       </c>
       <c r="Q17" t="str">
         <v>Clarkson</v>
@@ -1720,7 +1719,7 @@
         <v>007</v>
       </c>
       <c r="D18" t="str">
-        <v>RENEE A WILLIAMS</v>
+        <v>RENATA A WILLOUGHBY</v>
       </c>
       <c r="E18" t="str">
         <v>12 CHAMBORD DR</v>
@@ -1735,7 +1734,7 @@
         <v>14506</v>
       </c>
       <c r="I18" t="str">
-        <v>(585) 582-3139</v>
+        <v>(585) 555-0139</v>
       </c>
       <c r="J18" t="str">
         <v/>
@@ -1756,7 +1755,7 @@
         <v>24323</v>
       </c>
       <c r="P18" t="str">
-        <v>000120529</v>
+        <v>000910017</v>
       </c>
       <c r="Q18" t="str">
         <v>Mendon</v>
@@ -1797,10 +1796,10 @@
         <v>022</v>
       </c>
       <c r="D19" t="str">
-        <v>NICHOLAS E HUNTER</v>
+        <v>NICOLAS E HUNTLEY</v>
       </c>
       <c r="E19" t="str">
-        <v>226 SAN RON DR</v>
+        <v>226 SAN REMO DR</v>
       </c>
       <c r="F19" t="str">
         <v>WEBSTER</v>
@@ -1812,7 +1811,7 @@
         <v>14580</v>
       </c>
       <c r="I19" t="str">
-        <v>(585) 490-2175</v>
+        <v>(585) 555-0175</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -1833,7 +1832,7 @@
         <v>32647</v>
       </c>
       <c r="P19" t="str">
-        <v>000241474</v>
+        <v>000910018</v>
       </c>
       <c r="Q19" t="str">
         <v>Webster</v>
@@ -1874,7 +1873,7 @@
         <v>025</v>
       </c>
       <c r="D20" t="str">
-        <v>LALITH K GUNASINGHE</v>
+        <v>LALITH K GUNAWARDENA</v>
       </c>
       <c r="E20" t="str">
         <v>39 ESSEX DR</v>
@@ -1889,7 +1888,7 @@
         <v>14623</v>
       </c>
       <c r="I20" t="str">
-        <v>(585) 775-1398</v>
+        <v>(585) 555-0198</v>
       </c>
       <c r="J20" t="str">
         <v/>
@@ -1910,7 +1909,7 @@
         <v>25336</v>
       </c>
       <c r="P20" t="str">
-        <v>100068899</v>
+        <v>900110019</v>
       </c>
       <c r="Q20" t="str">
         <v>Henrietta</v>
@@ -1951,10 +1950,10 @@
         <v>015</v>
       </c>
       <c r="D21" t="str">
-        <v>MATTHEW J MCDERMOTT</v>
+        <v>MATTHIAS J MCDERRY</v>
       </c>
       <c r="E21" t="str">
-        <v>864 S GOODMAN ST</v>
+        <v>864 S GOODWIN ST</v>
       </c>
       <c r="F21" t="str">
         <v>ROCHESTER</v>
@@ -1966,7 +1965,7 @@
         <v>14620</v>
       </c>
       <c r="I21" t="str">
-        <v>256-1535</v>
+        <v>555-0135</v>
       </c>
       <c r="J21" t="str">
         <v/>
@@ -1987,7 +1986,7 @@
         <v>26516</v>
       </c>
       <c r="P21" t="str">
-        <v>008671694</v>
+        <v>008910020</v>
       </c>
       <c r="Q21" t="str">
         <v>LD 024</v>
